--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_3_27.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_3_27.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1458310.9006958</v>
+        <v>1433871.263439752</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1152701.47695844</v>
+        <v>1151840.918742179</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14661815.69938023</v>
+        <v>14661612.74404855</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5930539.060527797</v>
+        <v>5930626.202297251</v>
       </c>
     </row>
     <row r="11">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>24.95505229511726</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>19.43037313025244</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
         <v>15.30273751513505</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -694,16 +694,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="S2" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>46.6824</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>46.38724422570589</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.917475759485163</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.170977004479174</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>22.26949182588285</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
     </row>
     <row r="5">
@@ -883,31 +883,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>241</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>200.3235106453875</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>190.1066023865956</v>
       </c>
     </row>
     <row r="6">
@@ -968,25 +968,25 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1013,19 +1013,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>45.28887413297245</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>168.0088550715604</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F8" t="n">
-        <v>6.876045741711437</v>
+        <v>196.9826481283071</v>
       </c>
       <c r="G8" t="n">
         <v>15.30273751513505</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y8" t="n">
-        <v>190.0940167431535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1253,22 +1253,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494253</v>
+        <v>11.01727716149734</v>
       </c>
       <c r="W9" t="n">
-        <v>3.778505492039412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -1369,19 +1369,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1405,19 +1405,19 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>112.2877629084735</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1484,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>116.2839353693508</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>241</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1557,13 +1557,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1639,25 +1639,25 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>145.3912560091964</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
@@ -1694,7 +1694,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>62.13484214871502</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>14.83685490770588</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>230.8476210749815</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -1910,31 +1910,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>107.8454026017448</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,28 +1958,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>71.04758922419722</v>
       </c>
     </row>
     <row r="19">
@@ -2040,16 +2040,16 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2077,22 +2077,22 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
-        <v>232.8062112150493</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>71.01467844038818</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>32.05810949509299</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
         <v>137.3435171632106</v>
@@ -2171,7 +2171,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>121.9551940726745</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3.26531605719669</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>21.15688084963065</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2390,22 +2390,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>73.00396571148937</v>
+        <v>0.8288647492796855</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,22 +2435,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2551,22 +2551,22 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>1.796910429596556</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2599,10 +2599,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>31.55269876424505</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2630,19 +2630,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>12.90925672556489</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,10 +2675,10 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>81.0053776549329</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2800,10 +2800,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2827,22 +2827,22 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.252730413756608</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>82.65239032439645</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2870,19 +2870,19 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>89.93914640865493</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2906,28 +2906,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3034,10 +3034,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>88.89195435515768</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>210.4758895704059</v>
+        <v>9.234466016111838</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -3061,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
         <v>223.0958495641314</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3116,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,16 +3143,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>20.65238242916609</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3161,10 +3161,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>84.56713651463427</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.796910429597907</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
     </row>
     <row r="36">
@@ -3341,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>3.749580224518764</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>91.23594430375044</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3502,16 +3502,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.796910429597907</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3547,10 +3547,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V38" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>149.3484215845126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>183.8842973311964</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
         <v>205.6826957773044</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3781,22 +3781,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>200.3235106453949</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="42">
@@ -3806,19 +3806,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>75.88966943080946</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
@@ -3827,7 +3827,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>32.5327296920134</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -3869,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3982,13 +3982,13 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -4018,22 +4018,22 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="45">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4061,13 +4061,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4091,10 +4091,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>77.9134115034406</v>
       </c>
       <c r="S45" t="n">
-        <v>81.90579899813864</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>200.1647286948216</v>
@@ -4106,13 +4106,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4134,52 +4134,52 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.39393939393941</v>
+        <v>26.68381369134799</v>
       </c>
       <c r="C2" t="n">
-        <v>51.39393939393941</v>
+        <v>26.68381369134799</v>
       </c>
       <c r="D2" t="n">
-        <v>51.39393939393941</v>
+        <v>26.68381369134799</v>
       </c>
       <c r="E2" t="n">
-        <v>51.39393939393941</v>
+        <v>26.68381369134799</v>
       </c>
       <c r="F2" t="n">
-        <v>31.76729986843189</v>
+        <v>19.73831294214452</v>
       </c>
       <c r="G2" t="n">
-        <v>16.30998924708335</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="H2" t="n">
-        <v>16.30998924708335</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="I2" t="n">
-        <v>16.30998924708335</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="J2" t="n">
-        <v>4.24</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="K2" t="n">
-        <v>4.24</v>
+        <v>55.11790488024824</v>
       </c>
       <c r="L2" t="n">
-        <v>56.71</v>
+        <v>108.0953086000985</v>
       </c>
       <c r="M2" t="n">
-        <v>56.71</v>
+        <v>108.0953086000985</v>
       </c>
       <c r="N2" t="n">
-        <v>109.18</v>
+        <v>108.0953086000985</v>
       </c>
       <c r="O2" t="n">
-        <v>159.53</v>
+        <v>161.0727123199487</v>
       </c>
       <c r="P2" t="n">
-        <v>212</v>
+        <v>214.050116039799</v>
       </c>
       <c r="Q2" t="n">
-        <v>212</v>
+        <v>214.050116039799</v>
       </c>
       <c r="R2" t="n">
-        <v>212</v>
+        <v>159.9970564337892</v>
       </c>
       <c r="S2" t="n">
-        <v>158.4646464646465</v>
+        <v>105.9439968277793</v>
       </c>
       <c r="T2" t="n">
-        <v>158.4646464646465</v>
+        <v>105.9439968277793</v>
       </c>
       <c r="U2" t="n">
-        <v>158.4646464646465</v>
+        <v>51.89093722176946</v>
       </c>
       <c r="V2" t="n">
-        <v>158.4646464646465</v>
+        <v>51.89093722176946</v>
       </c>
       <c r="W2" t="n">
-        <v>158.4646464646465</v>
+        <v>51.89093722176946</v>
       </c>
       <c r="X2" t="n">
-        <v>158.4646464646465</v>
+        <v>51.89093722176946</v>
       </c>
       <c r="Y2" t="n">
-        <v>104.9292929292929</v>
+        <v>51.89093722176946</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>212</v>
+        <v>59.08819457959154</v>
       </c>
       <c r="C3" t="n">
-        <v>212</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="D3" t="n">
-        <v>158.4646464646465</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="E3" t="n">
-        <v>111.3107070707071</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="F3" t="n">
-        <v>111.3107070707071</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="G3" t="n">
-        <v>57.77535353535354</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="H3" t="n">
-        <v>4.24</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="I3" t="n">
-        <v>4.24</v>
+        <v>5.035134973581694</v>
       </c>
       <c r="J3" t="n">
-        <v>4.24</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="K3" t="n">
-        <v>4.24</v>
+        <v>57.25840604064623</v>
       </c>
       <c r="L3" t="n">
-        <v>4.24</v>
+        <v>57.25840604064623</v>
       </c>
       <c r="M3" t="n">
-        <v>56.71</v>
+        <v>110.2358097604965</v>
       </c>
       <c r="N3" t="n">
-        <v>107.06</v>
+        <v>161.0727123199487</v>
       </c>
       <c r="O3" t="n">
-        <v>159.53</v>
+        <v>214.050116039799</v>
       </c>
       <c r="P3" t="n">
-        <v>159.53</v>
+        <v>214.050116039799</v>
       </c>
       <c r="Q3" t="n">
-        <v>212</v>
+        <v>214.050116039799</v>
       </c>
       <c r="R3" t="n">
-        <v>212</v>
+        <v>159.9970564337892</v>
       </c>
       <c r="S3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="T3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="U3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="V3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="W3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="X3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
       <c r="Y3" t="n">
-        <v>212</v>
+        <v>113.1412541856014</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.269789723114</v>
+        <v>27.95824356358591</v>
       </c>
       <c r="C4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="D4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="E4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="F4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="G4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="H4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="I4" t="n">
-        <v>80.269789723114</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="J4" t="n">
-        <v>26.73443618776046</v>
+        <v>26.77543850855644</v>
       </c>
       <c r="K4" t="n">
-        <v>4.24</v>
+        <v>4.28100232079598</v>
       </c>
       <c r="L4" t="n">
-        <v>31.55412500771298</v>
+        <v>31.59512732850896</v>
       </c>
       <c r="M4" t="n">
-        <v>70.74216319993516</v>
+        <v>70.78316552073113</v>
       </c>
       <c r="N4" t="n">
-        <v>114.4330138553715</v>
+        <v>114.4740161761674</v>
       </c>
       <c r="O4" t="n">
-        <v>138.7722904902707</v>
+        <v>138.8132928110667</v>
       </c>
       <c r="P4" t="n">
-        <v>138.7722904902707</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="Q4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="R4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="S4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="T4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="U4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="V4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="W4" t="n">
-        <v>85.2369369549172</v>
+        <v>136.0643627756056</v>
       </c>
       <c r="X4" t="n">
-        <v>85.2369369549172</v>
+        <v>82.01130316959576</v>
       </c>
       <c r="Y4" t="n">
-        <v>85.2369369549172</v>
+        <v>27.95824356358591</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>761.6530195501136</v>
+        <v>528.5815077689649</v>
       </c>
       <c r="C5" t="n">
-        <v>761.6530195501136</v>
+        <v>285.1327311248648</v>
       </c>
       <c r="D5" t="n">
-        <v>761.6530195501136</v>
+        <v>41.68395448076474</v>
       </c>
       <c r="E5" t="n">
-        <v>761.6530195501136</v>
+        <v>41.68395448076474</v>
       </c>
       <c r="F5" t="n">
-        <v>518.2186761157702</v>
+        <v>34.73845373156126</v>
       </c>
       <c r="G5" t="n">
-        <v>274.7843326814268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H5" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>761.6530195501136</v>
+        <v>772.0302844130649</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="C6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L6" t="n">
-        <v>178.8354414866706</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M6" t="n">
-        <v>417.4254414866706</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N6" t="n">
-        <v>656.0154414866706</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O6" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S6" t="n">
-        <v>862.8304705528857</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="T6" t="n">
-        <v>660.6438759116518</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="U6" t="n">
-        <v>432.4202576480408</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="V6" t="n">
-        <v>262.7143434343434</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="W6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="X6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>285.1171548048954</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C8" t="n">
-        <v>41.68281137055202</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D8" t="n">
-        <v>41.68281137055202</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E8" t="n">
-        <v>41.68281137055202</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F8" t="n">
-        <v>34.73731062134854</v>
+        <v>34.73845373156126</v>
       </c>
       <c r="G8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X8" t="n">
-        <v>720.5656565656566</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y8" t="n">
-        <v>528.5514982392389</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>249.2431058683491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M9" t="n">
-        <v>487.8331058683492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N9" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O9" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S9" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T9" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U9" t="n">
-        <v>259.0029130987097</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V9" t="n">
-        <v>23.85080486696694</v>
+        <v>678.3417187247995</v>
       </c>
       <c r="W9" t="n">
-        <v>20.03413265278571</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="X9" t="n">
-        <v>20.03413265278571</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F11" t="n">
-        <v>19.28</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G11" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S11" t="n">
-        <v>601.4856691642474</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T11" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U11" t="n">
-        <v>132.7019827358318</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>249.2431058683491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M12" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N12" t="n">
-        <v>711.9619638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O12" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T12" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U12" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V12" t="n">
-        <v>846.5414794248982</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W12" t="n">
-        <v>603.1071359905548</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X12" t="n">
-        <v>395.2556357850219</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y12" t="n">
-        <v>187.495337020068</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I13" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J13" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="C14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="D14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="E14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="F14" t="n">
-        <v>19.28</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G14" t="n">
-        <v>19.28</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>122.6103673676048</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V14" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="X14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C15" t="n">
-        <v>817.1401454452562</v>
+        <v>789.6041262295092</v>
       </c>
       <c r="D15" t="n">
-        <v>668.2057357840049</v>
+        <v>640.669716568258</v>
       </c>
       <c r="E15" t="n">
-        <v>508.9682807785495</v>
+        <v>481.4322615628025</v>
       </c>
       <c r="F15" t="n">
-        <v>362.4337228054344</v>
+        <v>334.8977035896875</v>
       </c>
       <c r="G15" t="n">
-        <v>223.7028973880499</v>
+        <v>196.166878172303</v>
       </c>
       <c r="H15" t="n">
-        <v>110.3337617956292</v>
+        <v>82.7977425798823</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M15" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N15" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O15" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P15" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y16" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F17" t="n">
-        <v>730.820584772746</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="G17" t="n">
-        <v>487.3862413384025</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H17" t="n">
-        <v>243.9518979040591</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I17" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>587.9331627743991</v>
+        <v>110.334904905842</v>
       </c>
       <c r="C18" t="n">
-        <v>413.4801334932721</v>
+        <v>110.334904905842</v>
       </c>
       <c r="D18" t="n">
-        <v>413.4801334932721</v>
+        <v>110.334904905842</v>
       </c>
       <c r="E18" t="n">
-        <v>304.5453833904995</v>
+        <v>110.334904905842</v>
       </c>
       <c r="F18" t="n">
-        <v>158.0108254173845</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G18" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H18" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I18" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L18" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M18" t="n">
-        <v>304.1765223866491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N18" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O18" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T18" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U18" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V18" t="n">
-        <v>964</v>
+        <v>425.5489231905453</v>
       </c>
       <c r="W18" t="n">
-        <v>964</v>
+        <v>182.1001465464452</v>
       </c>
       <c r="X18" t="n">
-        <v>756.1484997944672</v>
+        <v>182.1001465464452</v>
       </c>
       <c r="Y18" t="n">
-        <v>756.1484997944672</v>
+        <v>110.334904905842</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="C20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="D20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="E20" t="n">
-        <v>953.9083846317729</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="F20" t="n">
-        <v>718.7505955256626</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="G20" t="n">
-        <v>475.3162520913191</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H20" t="n">
-        <v>231.8819086569757</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S20" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="U20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="V20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="W20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="X20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="Y20" t="n">
-        <v>953.9083846317729</v>
+        <v>730.8505943024719</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>554.0531065938121</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="C21" t="n">
-        <v>554.0531065938121</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="D21" t="n">
-        <v>554.0531065938121</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="E21" t="n">
-        <v>394.8156515883566</v>
+        <v>508.2152912359765</v>
       </c>
       <c r="F21" t="n">
-        <v>362.4337228054344</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G21" t="n">
-        <v>223.7028973880499</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>374.6006659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="U21" t="n">
-        <v>761.813405358766</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="V21" t="n">
-        <v>761.813405358766</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="W21" t="n">
-        <v>761.813405358766</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="X21" t="n">
-        <v>761.813405358766</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="Y21" t="n">
-        <v>554.0531065938121</v>
+        <v>667.4527462414319</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="G22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>752.8686165795576</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T23" t="n">
-        <v>527.5192735854855</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="U23" t="n">
-        <v>284.0849301511421</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="V23" t="n">
-        <v>40.65058671679864</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="W23" t="n">
-        <v>19.28</v>
+        <v>509.4769954460863</v>
       </c>
       <c r="X23" t="n">
-        <v>19.28</v>
+        <v>509.4769954460863</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.28</v>
+        <v>509.4769954460863</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>183.3210086493984</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="C24" t="n">
-        <v>183.3210086493984</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="D24" t="n">
-        <v>183.3210086493984</v>
+        <v>305.3837636211968</v>
       </c>
       <c r="E24" t="n">
-        <v>109.5796291428435</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F24" t="n">
-        <v>109.5796291428435</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G24" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M24" t="n">
-        <v>374.6006659261865</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>862.8304705528857</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T24" t="n">
-        <v>862.8304705528857</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U24" t="n">
-        <v>634.6068522892747</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V24" t="n">
-        <v>634.6068522892747</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="W24" t="n">
-        <v>391.1725088549313</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="X24" t="n">
-        <v>183.3210086493984</v>
+        <v>454.3181732824481</v>
       </c>
       <c r="Y24" t="n">
-        <v>183.3210086493984</v>
+        <v>454.3181732824481</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E26" t="n">
-        <v>720.5656565656591</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F26" t="n">
-        <v>718.7505955256626</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G26" t="n">
-        <v>475.3162520913191</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H26" t="n">
-        <v>231.8819086569757</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964.0000000000025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964.0000000000025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964.0000000000025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>964.0000000000025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>964.0000000000025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>964.0000000000025</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y26" t="n">
-        <v>720.5656565656591</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.28</v>
+        <v>521.2549444941228</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>521.2549444941228</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>521.2549444941228</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>508.2152912359765</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N27" t="n">
-        <v>711.9619638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U27" t="n">
-        <v>259.0029130987097</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V27" t="n">
-        <v>259.0029130987097</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="W27" t="n">
-        <v>259.0029130987097</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="X27" t="n">
-        <v>51.15141289317683</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="Y27" t="n">
-        <v>51.15141289317683</v>
+        <v>689.4702815141908</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>569.2254314512334</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964.000000000002</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S29" t="n">
-        <v>752.8686165795522</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T29" t="n">
-        <v>749.5830303030303</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="U29" t="n">
-        <v>506.1486868686869</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="V29" t="n">
-        <v>262.7143434343434</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="W29" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="X29" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>812.6742080953335</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102.7672629539358</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>453.2824885506521</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>453.2824885506521</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>453.2824885506521</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N30" t="n">
-        <v>781.3565223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T30" t="n">
-        <v>761.813405358766</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U30" t="n">
-        <v>761.813405358766</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V30" t="n">
-        <v>761.813405358766</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="W30" t="n">
-        <v>518.3790619244226</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="X30" t="n">
-        <v>310.5275617188897</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="Y30" t="n">
-        <v>102.7672629539358</v>
+        <v>627.7355178317791</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>577.1760942224001</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="C32" t="n">
-        <v>333.7417507880567</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="D32" t="n">
-        <v>333.7417507880567</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="E32" t="n">
-        <v>333.7417507880567</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="F32" t="n">
-        <v>333.7417507880567</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="G32" t="n">
-        <v>333.7417507880567</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="H32" t="n">
-        <v>243.9518979040591</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="I32" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>953.908384631775</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>802.5254372164723</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>802.5254372164723</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T32" t="n">
-        <v>577.1760942224001</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U32" t="n">
-        <v>577.1760942224001</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V32" t="n">
-        <v>577.1760942224001</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="W32" t="n">
-        <v>577.1760942224001</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="X32" t="n">
-        <v>577.1760942224001</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="Y32" t="n">
-        <v>577.1760942224001</v>
+        <v>284.1276524520142</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>258.5140388040948</v>
+        <v>502.6601697108322</v>
       </c>
       <c r="C33" t="n">
-        <v>258.5140388040948</v>
+        <v>328.2071404297052</v>
       </c>
       <c r="D33" t="n">
-        <v>109.5796291428435</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="E33" t="n">
-        <v>109.5796291428435</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F33" t="n">
-        <v>109.5796291428435</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G33" t="n">
-        <v>109.5796291428435</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H33" t="n">
-        <v>109.5796291428435</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M33" t="n">
-        <v>304.1765223866491</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>466.3655390096276</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>466.3655390096276</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W33" t="n">
-        <v>466.3655390096276</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X33" t="n">
-        <v>258.5140388040948</v>
+        <v>878.6358054958541</v>
       </c>
       <c r="Y33" t="n">
-        <v>258.5140388040948</v>
+        <v>670.8755067309003</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>475.3162520913191</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C35" t="n">
-        <v>475.3162520913191</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D35" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E35" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F35" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G35" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964.0000000000039</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>718.7505955256626</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W35" t="n">
-        <v>718.7505955256626</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X35" t="n">
-        <v>475.3162520913191</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y35" t="n">
-        <v>475.3162520913191</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>417.2095324773084</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="C36" t="n">
-        <v>417.2095324773084</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="D36" t="n">
-        <v>417.2095324773084</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="E36" t="n">
-        <v>257.9720774718529</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F36" t="n">
-        <v>111.4375194987378</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G36" t="n">
-        <v>111.4375194987378</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>248.2299999999999</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>486.8199999999999</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N36" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O36" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V36" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W36" t="n">
-        <v>417.2095324773084</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X36" t="n">
-        <v>417.2095324773084</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y36" t="n">
-        <v>417.2095324773084</v>
+        <v>512.7568786610034</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C38" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D38" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E38" t="n">
-        <v>475.3162520913191</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F38" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G38" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2389935105028</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951613</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580655</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.1449945653048</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.3399447079529</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964.0000000000039</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>962.184938960006</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V38" t="n">
-        <v>718.7505955256626</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W38" t="n">
-        <v>718.7505955256626</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X38" t="n">
-        <v>718.7505955256626</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y38" t="n">
-        <v>718.7505955256626</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>344.5900207806347</v>
+        <v>194.4883050441255</v>
       </c>
       <c r="C39" t="n">
-        <v>170.1369914995077</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D39" t="n">
-        <v>170.1369914995077</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N39" t="n">
-        <v>726.4231058683491</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O39" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>964</v>
+        <v>778.3154410346802</v>
       </c>
       <c r="V39" t="n">
-        <v>964</v>
+        <v>778.3154410346802</v>
       </c>
       <c r="W39" t="n">
-        <v>720.5656565656566</v>
+        <v>778.3154410346802</v>
       </c>
       <c r="X39" t="n">
-        <v>720.5656565656566</v>
+        <v>570.4639408291474</v>
       </c>
       <c r="Y39" t="n">
-        <v>512.8053578007027</v>
+        <v>362.7036420641935</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y40" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>964.0000000000075</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V41" t="n">
-        <v>518.2186761157702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W41" t="n">
-        <v>274.7843326814268</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X41" t="n">
-        <v>31.34998924708335</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y41" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>588.024364214978</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="C42" t="n">
-        <v>588.024364214978</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="D42" t="n">
-        <v>439.0899545537268</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="E42" t="n">
-        <v>439.0899545537268</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="F42" t="n">
-        <v>362.4337228054344</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="G42" t="n">
-        <v>223.7028973880499</v>
+        <v>166.265754478665</v>
       </c>
       <c r="H42" t="n">
-        <v>110.3337617956292</v>
+        <v>52.8966188862443</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L42" t="n">
-        <v>65.58652238664914</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M42" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N42" t="n">
-        <v>542.7665223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W42" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X42" t="n">
-        <v>964</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y42" t="n">
-        <v>756.2397012350461</v>
+        <v>304.9965798960495</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G44" t="n">
-        <v>31.34998924708335</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H44" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T44" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U44" t="n">
-        <v>761.6530195501136</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V44" t="n">
-        <v>761.6530195501136</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W44" t="n">
-        <v>518.2186761157702</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="X44" t="n">
-        <v>518.2186761157702</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y44" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>20.03413265278571</v>
+        <v>307.1033079837604</v>
       </c>
       <c r="C45" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="D45" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="E45" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="F45" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G45" t="n">
-        <v>20.03413265278571</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H45" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L45" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M45" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N45" t="n">
-        <v>725.41</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O45" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>885.3567398505952</v>
       </c>
       <c r="S45" t="n">
-        <v>881.2668696988499</v>
+        <v>885.3567398505952</v>
       </c>
       <c r="T45" t="n">
-        <v>679.0802750576159</v>
+        <v>683.1701452093612</v>
       </c>
       <c r="U45" t="n">
-        <v>679.0802750576159</v>
+        <v>683.1701452093612</v>
       </c>
       <c r="V45" t="n">
-        <v>679.0802750576159</v>
+        <v>683.1701452093612</v>
       </c>
       <c r="W45" t="n">
-        <v>435.6459316232725</v>
+        <v>683.1701452093612</v>
       </c>
       <c r="X45" t="n">
-        <v>227.7944314177396</v>
+        <v>475.3186450038284</v>
       </c>
       <c r="Y45" t="n">
-        <v>20.03413265278571</v>
+        <v>475.3186450038284</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y46" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7959,22 +7959,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>220.0898510449805</v>
+        <v>271.4402576706899</v>
       </c>
       <c r="L2" t="n">
-        <v>288.7664149699872</v>
+        <v>289.278943979937</v>
       </c>
       <c r="M2" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N2" t="n">
-        <v>282.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O2" t="n">
-        <v>280.9567972802726</v>
+        <v>283.6107404316365</v>
       </c>
       <c r="P2" t="n">
-        <v>284.2329957552695</v>
+        <v>284.7455247652193</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8038,25 +8038,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>137.841438974359</v>
+        <v>191.3539679843088</v>
       </c>
       <c r="L3" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>195.1340339220183</v>
+        <v>195.6465629319681</v>
       </c>
       <c r="N3" t="n">
-        <v>182.2002979419192</v>
+        <v>182.6921187090427</v>
       </c>
       <c r="O3" t="n">
-        <v>195.5962444444444</v>
+        <v>196.1087734543942</v>
       </c>
       <c r="P3" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q3" t="n">
-        <v>192.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8278,16 +8278,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L6" t="n">
-        <v>173.0976943544532</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>174.6270615612551</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P6" t="n">
         <v>133.9744074143302</v>
@@ -8442,7 +8442,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N8" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O8" t="n">
         <v>380.8001812627454</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L9" t="n">
-        <v>370.8403453034592</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>368.9890303080512</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q9" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8685,7 +8685,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
-        <v>370.8403453034592</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M12" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N12" t="n">
-        <v>357.73449794694</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P12" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q12" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8907,13 +8907,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M14" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N14" t="n">
         <v>437.3469244119842</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L15" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>368.9890303080512</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q15" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9144,10 +9144,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M17" t="n">
         <v>449.5135334928325</v>
@@ -9229,13 +9229,13 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>303.2845009208181</v>
+        <v>303.312501347746</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
         <v>318.4627686399372</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,19 +9466,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>231.1106999087204</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9633,7 +9633,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P23" t="n">
-        <v>321.7421299892443</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9700,22 +9700,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>370.8403453034592</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.7421299892392</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9940,19 +9940,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>357.73449794694</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892388</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10177,19 +10177,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>301.2062135585481</v>
+        <v>231.1529892133073</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7421299892388</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10414,13 +10414,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>372.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299892407</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,22 +10645,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>369.8170060425004</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889227</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10888,19 +10888,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>383.1340339220183</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>382.5729051834858</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11055,7 +11055,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>321.7421299892443</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,19 +11119,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>185.3286448168935</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
@@ -11292,7 +11292,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P44" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11356,22 +11356,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L45" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>371.3183728223746</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
         <v>139.9817740860215</v>
@@ -23227,19 +23227,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>406.8760457417114</v>
+        <v>176.0015501456288</v>
       </c>
       <c r="G11" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H11" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I11" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23263,19 +23263,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>215.4644955616614</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23294,7 +23294,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
         <v>172.7084989883157</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>116.5166517800745</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>10.69498316091961</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,13 +23415,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H14" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23497,25 +23497,25 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
-        <v>225.4551947762062</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>347.4314726443769</v>
       </c>
       <c r="X14" t="n">
         <v>369.731100678469</v>
@@ -23534,7 +23534,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>27.31724297911936</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23552,7 +23552,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>27.26179070270006</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>140.6136200195524</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
         <v>86.16204325169439</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>176.02842466673</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G17" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>10.13979328157632</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23768,31 +23768,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>49.79967785365611</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>205.6826957773044</v>
+        <v>134.6351065531071</v>
       </c>
     </row>
     <row r="19">
@@ -23898,7 +23898,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
@@ -23907,7 +23907,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
@@ -23935,22 +23935,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
-        <v>174.0698345266622</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23974,13 +23974,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>152.0811711237432</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -24017,7 +24017,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>113.0111028982909</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -24029,7 +24029,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24056,10 +24056,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>78.20953462214715</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
@@ -24074,7 +24074,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24102,7 +24102,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H22" t="n">
-        <v>29.04020492207155</v>
+        <v>29.04020492207158</v>
       </c>
       <c r="I22" t="n">
         <v>155.4504749272583</v>
@@ -24163,13 +24163,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>379.4685256062839</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
@@ -24181,7 +24181,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
@@ -24217,16 +24217,16 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>328.0840878677824</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24248,22 +24248,22 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>84.64111474391157</v>
+        <v>156.8162157061213</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -24293,22 +24293,22 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -24409,22 +24409,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>405.0791353121149</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>108.6003065196844</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24457,10 +24457,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>134.9804848856223</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24488,19 +24488,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>144.7358237298361</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -24533,10 +24533,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24545,7 +24545,7 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C28" t="n">
         <v>167.2468210986278</v>
@@ -24573,7 +24573,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
         <v>162.2271725074396</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>284.2675141160747</v>
       </c>
       <c r="D29" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24658,10 +24658,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24685,22 +24685,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>219.8431191503747</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
         <v>369.731100678469</v>
@@ -24719,7 +24719,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>90.05610866391929</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24728,19 +24728,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>55.13006598472894</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,28 +24764,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24877,10 +24877,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
@@ -24892,10 +24892,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>250.5828477606095</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>201.2414235542941</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24919,13 +24919,13 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -24934,7 +24934,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24953,16 +24953,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
@@ -24974,10 +24974,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>205.2889996518087</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25019,10 +25019,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>121.2058486888432</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25044,7 +25044,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756322</v>
       </c>
       <c r="G34" t="n">
         <v>167.9909793584588</v>
@@ -25077,7 +25077,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
         <v>177.2933913771695</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>239.4980740029174</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25117,7 +25117,7 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.193788784946896</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>173.9525530126115</v>
       </c>
     </row>
     <row r="36">
@@ -25199,22 +25199,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>153.8955002308822</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>20.99949993274602</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25238,13 +25238,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -25253,10 +25253,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25332,10 +25332,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25348,7 +25348,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
@@ -25360,16 +25360,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G38" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -25393,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.193788784946896</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
@@ -25405,10 +25405,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V38" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25436,7 +25436,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>8.296658870888336</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25484,16 +25484,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>42.05708474977843</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -25521,7 +25521,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309076</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
@@ -25575,7 +25575,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="41">
@@ -25600,7 +25600,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25609,7 +25609,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25639,22 +25639,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>22.77233891873644</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X41" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="42">
@@ -25664,19 +25664,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>69.17954296257442</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25685,7 +25685,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>56.86390315940168</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25727,10 +25727,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25822,7 +25822,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C44" t="n">
         <v>365.2728917710076</v>
@@ -25840,13 +25840,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H44" t="n">
-        <v>339.4748021157671</v>
+        <v>127.189416472325</v>
       </c>
       <c r="I44" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25867,7 +25867,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
         <v>149.8691179411497</v>
@@ -25876,22 +25876,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>32.76303813328863</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W44" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X44" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y44" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="45">
@@ -25901,10 +25901,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>147.4450655646388</v>
@@ -25919,13 +25919,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25949,10 +25949,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>100.1578341526431</v>
+        <v>22.24442264920253</v>
       </c>
       <c r="S45" t="n">
-        <v>89.77737210569919</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25964,13 +25964,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -25992,7 +25992,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F46" t="n">
-        <v>12.23408043756322</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
         <v>167.9909793584588</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>900910.8236589557</v>
+        <v>900929.3927402981</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>907722.1206286527</v>
+        <v>907722.6383190203</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>907722.1206286527</v>
+        <v>907722.6383190203</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>382340.3914008602</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>382340.3914008602</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>382340.3914008602</v>
+        <v>382348.1816572802</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>382340.3914008602</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>382340.3914008609</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>382340.3914008603</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>382340.3914008603</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>382340.3914008604</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>382340.3914008606</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>382340.3914008607</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>382340.391400861</v>
+        <v>382348.1816572802</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>382340.3914008602</v>
+        <v>382348.1816572801</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>554203.1946583914</v>
+        <v>554203.1946583916</v>
       </c>
       <c r="C2" t="n">
-        <v>554203.1946583913</v>
+        <v>554203.1946583912</v>
       </c>
       <c r="D2" t="n">
-        <v>554203.1946583915</v>
+        <v>554203.1946583912</v>
       </c>
       <c r="E2" t="n">
-        <v>224312.3414223356</v>
+        <v>224316.9079172986</v>
       </c>
       <c r="F2" t="n">
-        <v>224312.3414223356</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="G2" t="n">
-        <v>224312.3414223356</v>
+        <v>224316.9079172986</v>
       </c>
       <c r="H2" t="n">
-        <v>224312.3414223356</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="I2" t="n">
-        <v>224312.3414223359</v>
+        <v>224316.9079172986</v>
       </c>
       <c r="J2" t="n">
-        <v>224312.3414223357</v>
+        <v>224316.9079172988</v>
       </c>
       <c r="K2" t="n">
-        <v>224312.3414223357</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="L2" t="n">
-        <v>224312.3414223357</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="M2" t="n">
-        <v>224312.3414223357</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="N2" t="n">
-        <v>224312.3414223358</v>
+        <v>224316.9079172986</v>
       </c>
       <c r="O2" t="n">
-        <v>224312.341422336</v>
+        <v>224316.9079172987</v>
       </c>
       <c r="P2" t="n">
-        <v>224312.3414223356</v>
+        <v>224316.9079172987</v>
       </c>
     </row>
     <row r="3">
@@ -26313,10 +26313,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17761.519</v>
+        <v>17933.27925940139</v>
       </c>
       <c r="C3" t="n">
-        <v>60737.28896800001</v>
+        <v>60576.32218666811</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>13867.132</v>
+        <v>14001.23214027929</v>
       </c>
       <c r="K3" t="n">
-        <v>48385.184</v>
+        <v>48256.95293363261</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>348087.6000689332</v>
+        <v>350176.5876421471</v>
       </c>
       <c r="C4" t="n">
-        <v>304231.1291436085</v>
+        <v>307255.7689654693</v>
       </c>
       <c r="D4" t="n">
-        <v>304231.1291436085</v>
+        <v>307255.7689654693</v>
       </c>
       <c r="E4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="F4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="G4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="H4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="I4" t="n">
-        <v>25281.74016844441</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="J4" t="n">
-        <v>25281.74016844438</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="K4" t="n">
-        <v>25281.74016844438</v>
+        <v>28310.24133100991</v>
       </c>
       <c r="L4" t="n">
-        <v>25281.74016844438</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="M4" t="n">
-        <v>25281.74016844439</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="N4" t="n">
-        <v>25281.74016844439</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="O4" t="n">
-        <v>25281.74016844441</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="P4" t="n">
-        <v>25281.74016844436</v>
+        <v>28310.24133100992</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36850</v>
+        <v>36881.16176380494</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>151504.0755894582</v>
+        <v>149212.1659930382</v>
       </c>
       <c r="C6" t="n">
-        <v>140954.3765467828</v>
+        <v>138089.8347424921</v>
       </c>
       <c r="D6" t="n">
-        <v>201691.665514783</v>
+        <v>198666.1569291602</v>
       </c>
       <c r="E6" t="n">
-        <v>184377.8012538912</v>
+        <v>181352.997822527</v>
       </c>
       <c r="F6" t="n">
-        <v>184377.8012538912</v>
+        <v>181352.9978225271</v>
       </c>
       <c r="G6" t="n">
-        <v>184377.8012538912</v>
+        <v>181352.997822527</v>
       </c>
       <c r="H6" t="n">
-        <v>184377.8012538912</v>
+        <v>181352.9978225271</v>
       </c>
       <c r="I6" t="n">
-        <v>184377.8012538916</v>
+        <v>181352.997822527</v>
       </c>
       <c r="J6" t="n">
-        <v>170510.6692538913</v>
+        <v>167351.7656822479</v>
       </c>
       <c r="K6" t="n">
-        <v>135992.6172538913</v>
+        <v>133096.0448888945</v>
       </c>
       <c r="L6" t="n">
-        <v>184377.8012538913</v>
+        <v>181352.9978225271</v>
       </c>
       <c r="M6" t="n">
-        <v>184377.8012538914</v>
+        <v>181352.9978225271</v>
       </c>
       <c r="N6" t="n">
-        <v>184377.8012538914</v>
+        <v>181352.997822527</v>
       </c>
       <c r="O6" t="n">
-        <v>184377.8012538916</v>
+        <v>181352.9978225271</v>
       </c>
       <c r="P6" t="n">
-        <v>184377.8012538912</v>
+        <v>181352.9978225271</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,13 +26840,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -26867,22 +26867,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,10 +26892,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="C4" t="n">
-        <v>188</v>
+        <v>187.5017598677093</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="K4" t="n">
-        <v>188</v>
+        <v>187.5017598677093</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,10 +27185,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="K4" t="n">
-        <v>188</v>
+        <v>187.5017598677093</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27301,7 +27301,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>329.7338416634806</v>
+        <v>357.7787893683633</v>
       </c>
       <c r="C2" t="n">
         <v>365.2728917710076</v>
@@ -27313,7 +27313,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>387.445672611459</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27325,7 +27325,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27349,16 +27349,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>149.8691179411497</v>
+        <v>96.35658893119992</v>
       </c>
       <c r="S2" t="n">
-        <v>156.0200695862453</v>
+        <v>155.5075405762956</v>
       </c>
       <c r="T2" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3456529078365</v>
+        <v>197.8331238978867</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -27370,7 +27370,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
-        <v>333.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="3">
@@ -27380,31 +27380,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498673</v>
+        <v>113.0206546399176</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>119.195969978366</v>
       </c>
       <c r="D3" t="n">
-        <v>94.44506556463875</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>110.9626804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>84.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>59.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -27428,10 +27428,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>100.1578341526431</v>
+        <v>46.64530514269338</v>
       </c>
       <c r="S3" t="n">
-        <v>171.6831711038378</v>
+        <v>125.2959268781319</v>
       </c>
       <c r="T3" t="n">
         <v>200.1647286948216</v>
@@ -27459,10 +27459,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>174.9145044224521</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C4" t="n">
-        <v>167.2468210986278</v>
+        <v>166.0758440941487</v>
       </c>
       <c r="D4" t="n">
         <v>148.6154730182124</v>
@@ -27483,7 +27483,7 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
-        <v>40.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27501,10 +27501,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
         <v>177.2933913771695</v>
@@ -27525,10 +27525,10 @@
         <v>286.522998336591</v>
       </c>
       <c r="X4" t="n">
-        <v>225.7096553890372</v>
+        <v>172.1971263790874</v>
       </c>
       <c r="Y4" t="n">
-        <v>218.5846533520948</v>
+        <v>165.072124342145</v>
       </c>
     </row>
     <row r="5">
@@ -27538,31 +27538,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C5" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D5" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E5" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>165.8760457417114</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>174.302737515135</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -27592,7 +27592,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>22.77233891874386</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
         <v>251.3456529078365</v>
@@ -27607,7 +27607,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560536</v>
+        <v>196.131336269458</v>
       </c>
     </row>
     <row r="6">
@@ -27623,25 +27623,25 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -27668,19 +27668,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>126.3942969708654</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>64.79173207786485</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
         <v>205.7729852034775</v>
@@ -27699,7 +27699,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C7" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D7" t="n">
         <v>148.6154730182124</v>
@@ -27738,16 +27738,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
-        <v>179.7131144384051</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T7" t="n">
         <v>227.9455894282815</v>
@@ -27775,19 +27775,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C8" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>209.8933976134044</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
@@ -27841,10 +27841,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y8" t="n">
-        <v>196.1439219129001</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -27878,7 +27878,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -27908,22 +27908,22 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>221.7833099879279</v>
       </c>
       <c r="W9" t="n">
-        <v>247.9164776688802</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -34614,22 +34614,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>51.35040662570935</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>50.85858585858585</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="P2" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34693,25 +34693,25 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="N3" t="n">
-        <v>50.85858585858586</v>
+        <v>51.35040662570936</v>
       </c>
       <c r="O3" t="n">
-        <v>53</v>
+        <v>53.51252900994975</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -34851,13 +34851,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M5" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N5" t="n">
         <v>207.9338608153932</v>
@@ -34933,16 +34933,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L6" t="n">
-        <v>34.54331457457899</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -35097,7 +35097,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N8" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O8" t="n">
         <v>150.7019698410586</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L9" t="n">
-        <v>232.285965523585</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O9" t="n">
-        <v>226.3927858636067</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35334,13 +35334,13 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N11" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O11" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P11" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
-        <v>232.285965523585</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N12" t="n">
-        <v>226.3927858636067</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P12" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35568,7 +35568,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M14" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N14" t="n">
         <v>207.9338608153932</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L15" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>226.3927858636067</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q15" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35884,13 +35884,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>161.1504669987997</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
         <v>184.4883612256069</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,19 +36121,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>99.76898782538704</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P23" t="n">
-        <v>90.50913423397475</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36355,22 +36355,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>232.285965523585</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36525,7 +36525,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.5091342339697</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36595,19 +36595,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>226.3927858636067</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396923</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36832,19 +36832,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>169.8645014752148</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.50913423396923</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37069,13 +37069,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
@@ -37227,7 +37227,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>90.50913423397108</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,22 +37300,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>231.2626262626262</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37458,7 +37458,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439422</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
@@ -37543,19 +37543,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>239.9766607390413</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37710,7 +37710,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>90.50913423397475</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,19 +37774,19 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>46.77426503701933</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
@@ -37944,10 +37944,10 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O44" t="n">
-        <v>150.7019698410586</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P44" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38011,22 +38011,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L45" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>239.9766607390412</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
